--- a/my_words.xlsx
+++ b/my_words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiwi_\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BFA5A8-1B9D-4385-90DE-70A663C96031}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638DBBAF-0131-4400-8F10-6DB82119FDF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20378" windowHeight="8760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,30 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="443">
   <si>
     <t>en</t>
   </si>
   <si>
     <t>cn</t>
-  </si>
-  <si>
-    <t>Abandon</t>
-  </si>
-  <si>
-    <t>放弃</t>
-  </si>
-  <si>
-    <t>Brilliant</t>
-  </si>
-  <si>
-    <t>出色的</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>容量</t>
   </si>
   <si>
     <t>unit</t>
@@ -54,43 +36,1329 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>/ˈæpl/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B1-Unit One</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>/ˈbrɪljənt/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>/'kepaciti/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>type</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>phonetic</t>
+  </si>
+  <si>
+    <t>cry</t>
+  </si>
+  <si>
+    <t>哭；喊叫</t>
+  </si>
+  <si>
     <t>v.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>B1-Unit 1</t>
+  </si>
+  <si>
+    <t>/kraɪ/</t>
+  </si>
+  <si>
+    <t>drive</t>
+  </si>
+  <si>
+    <t>驾驶</t>
+  </si>
+  <si>
+    <t>/draɪv/</t>
+  </si>
+  <si>
+    <t>funny</t>
+  </si>
+  <si>
+    <t>滑稽的；有趣的</t>
   </si>
   <si>
     <t>adj.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/ˈfʌni/</t>
+  </si>
+  <si>
+    <t>hope</t>
+  </si>
+  <si>
+    <t>希望</t>
+  </si>
+  <si>
+    <t>/həʊp/</t>
+  </si>
+  <si>
+    <t>laugh</t>
+  </si>
+  <si>
+    <t>笑</t>
+  </si>
+  <si>
+    <t>/lɑːf/</t>
+  </si>
+  <si>
+    <t>nice</t>
+  </si>
+  <si>
+    <t>令人愉快的；亲切的</t>
+  </si>
+  <si>
+    <t>/naɪs/</t>
+  </si>
+  <si>
+    <t>smile</t>
+  </si>
+  <si>
+    <t>微笑</t>
+  </si>
+  <si>
+    <t>/smɪl/</t>
+  </si>
+  <si>
+    <t>strong</t>
+  </si>
+  <si>
+    <t>强壮的</t>
+  </si>
+  <si>
+    <t>/strɒŋ/</t>
+  </si>
+  <si>
+    <t>student</t>
+  </si>
+  <si>
+    <t>学生</t>
   </si>
   <si>
     <t>n.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/ˈstjuːdnt/</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>年轻的</t>
+  </si>
+  <si>
+    <t>/jʌŋ/</t>
+  </si>
+  <si>
+    <t>big</t>
+  </si>
+  <si>
+    <t>大的</t>
+  </si>
+  <si>
+    <t>/bɪɡ/</t>
+  </si>
+  <si>
+    <t>boy</t>
+  </si>
+  <si>
+    <t>男孩</t>
+  </si>
+  <si>
+    <t>/bɔɪ/</t>
+  </si>
+  <si>
+    <t>child</t>
+  </si>
+  <si>
+    <t>儿童</t>
+  </si>
+  <si>
+    <t>/tʃaɪld/</t>
+  </si>
+  <si>
+    <t>drink</t>
+  </si>
+  <si>
+    <t>喝</t>
+  </si>
+  <si>
+    <t>/drɪŋk/</t>
+  </si>
+  <si>
+    <t>eat</t>
+  </si>
+  <si>
+    <t>吃</t>
+  </si>
+  <si>
+    <t>/iːt/</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>女孩</t>
+  </si>
+  <si>
+    <t>/ɡɜːl/</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>男人</t>
+  </si>
+  <si>
+    <t>/mæn/</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>老的；旧的</t>
+  </si>
+  <si>
+    <t>/əʊld/</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>小的</t>
+  </si>
+  <si>
+    <t>/smɔːl/</t>
+  </si>
+  <si>
+    <t>woman</t>
+  </si>
+  <si>
+    <t>女人</t>
+  </si>
+  <si>
+    <t>/ˈwʊmən/</t>
+  </si>
+  <si>
+    <t>able</t>
+  </si>
+  <si>
+    <t>能够</t>
+  </si>
+  <si>
+    <t>B1-Unit 2</t>
+  </si>
+  <si>
+    <t>/ˈeɪbl/</t>
+  </si>
+  <si>
+    <t>alone</t>
+  </si>
+  <si>
+    <t>单独的</t>
+  </si>
+  <si>
+    <t>/əˈləʊn/</t>
+  </si>
+  <si>
+    <t>animal</t>
+  </si>
+  <si>
+    <t>动物</t>
+  </si>
+  <si>
+    <t>/ˈænɪml/</t>
+  </si>
+  <si>
+    <t>become</t>
+  </si>
+  <si>
+    <t>变成</t>
+  </si>
+  <si>
+    <t>/bɪˈkʌm/</t>
+  </si>
+  <si>
+    <t>call</t>
+  </si>
+  <si>
+    <t>呼唤；打电话</t>
+  </si>
+  <si>
+    <t>/kɔːl/</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>鱼</t>
+  </si>
+  <si>
+    <t>/fɪʃ/</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>自由的；免费的</t>
+  </si>
+  <si>
+    <t>/friː/</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>种；类；善良的</t>
+  </si>
+  <si>
+    <t>n./adj.</t>
+  </si>
+  <si>
+    <t>/kaɪnd/</t>
+  </si>
+  <si>
+    <t>relax</t>
+  </si>
+  <si>
+    <t>放松</t>
+  </si>
+  <si>
+    <t>/rɪˈlæks/</t>
+  </si>
+  <si>
+    <t>sea</t>
+  </si>
+  <si>
+    <t>海洋</t>
+  </si>
+  <si>
+    <t>/siː/</t>
+  </si>
+  <si>
+    <t>baby</t>
+  </si>
+  <si>
+    <t>婴儿</t>
+  </si>
+  <si>
+    <t>/ˈbeɪbi/</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>鸟</t>
+  </si>
+  <si>
+    <t>/bɜːd/</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>猫</t>
+  </si>
+  <si>
+    <t>/kæt/</t>
+  </si>
+  <si>
+    <t>dog</t>
+  </si>
+  <si>
+    <t>狗</t>
+  </si>
+  <si>
+    <t>/dɒɡ/</t>
+  </si>
+  <si>
+    <t>fly</t>
+  </si>
+  <si>
+    <t>飞</t>
+  </si>
+  <si>
+    <t>/flaɪ/</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>食物</t>
+  </si>
+  <si>
+    <t>/fuːd/</t>
+  </si>
+  <si>
+    <t>live</t>
+  </si>
+  <si>
+    <t>居住；生存</t>
+  </si>
+  <si>
+    <t>/lɪv/</t>
+  </si>
+  <si>
+    <t>nature</t>
+  </si>
+  <si>
+    <t>自然</t>
+  </si>
+  <si>
+    <t>/ˈneɪtʃə/</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+  </si>
+  <si>
+    <t>兔子</t>
+  </si>
+  <si>
+    <t>/ˈræbɪt/</t>
+  </si>
+  <si>
+    <t>zoo</t>
+  </si>
+  <si>
+    <t>动物园</t>
+  </si>
+  <si>
+    <t>/zuː/</t>
+  </si>
+  <si>
+    <t>burn</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>B1-Unit 3</t>
+  </si>
+  <si>
+    <t>/bɜːn/</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>检查</t>
+  </si>
+  <si>
+    <t>/tʃek/</t>
+  </si>
+  <si>
+    <t>dirty</t>
+  </si>
+  <si>
+    <t>脏的</t>
+  </si>
+  <si>
+    <t>/ˈdɜːti/</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>/ˈfaɪə/</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>健康</t>
+  </si>
+  <si>
+    <t>/helθ/</t>
+  </si>
+  <si>
+    <t>person</t>
+  </si>
+  <si>
+    <t>人</t>
+  </si>
+  <si>
+    <t>/ˈpɜːsn/</t>
+  </si>
+  <si>
+    <t>problem</t>
+  </si>
+  <si>
+    <t>问题</t>
+  </si>
+  <si>
+    <t>/ˈprɒbləm/</t>
+  </si>
+  <si>
+    <t>rule</t>
+  </si>
+  <si>
+    <t>规则</t>
+  </si>
+  <si>
+    <t>/ruːl/</t>
+  </si>
+  <si>
+    <t>smoke</t>
+  </si>
+  <si>
+    <t>烟</t>
+  </si>
+  <si>
+    <t>n./v.</t>
+  </si>
+  <si>
+    <t>/sməʊk/</t>
+  </si>
+  <si>
+    <t>understand</t>
+  </si>
+  <si>
+    <t>理解</t>
+  </si>
+  <si>
+    <t>/ˌʌndəˈstænd/</t>
+  </si>
+  <si>
+    <t>agree</t>
+  </si>
+  <si>
+    <t>同意</t>
+  </si>
+  <si>
+    <t>B1-Unit 4</t>
+  </si>
+  <si>
+    <t>/əˈɡriː/</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+  <si>
+    <t>清晰的</t>
+  </si>
+  <si>
+    <t>/klɪə/</t>
+  </si>
+  <si>
+    <t>close</t>
+  </si>
+  <si>
+    <t>关闭</t>
+  </si>
+  <si>
+    <t>/kləʊz/</t>
+  </si>
+  <si>
+    <t>help</t>
+  </si>
+  <si>
+    <t>帮助</t>
+  </si>
+  <si>
+    <t>/help/</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>意思是</t>
+  </si>
+  <si>
+    <t>/miːn/</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>/ˈkwestʃən/</t>
+  </si>
+  <si>
+    <t>read</t>
+  </si>
+  <si>
+    <t>阅读</t>
+  </si>
+  <si>
+    <t>/riːd/</t>
+  </si>
+  <si>
+    <t>say</t>
+  </si>
+  <si>
+    <t>说</t>
+  </si>
+  <si>
+    <t>/seɪ/</t>
+  </si>
+  <si>
+    <t>use</t>
+  </si>
+  <si>
+    <t>使用</t>
+  </si>
+  <si>
+    <t>/juːz/</t>
+  </si>
+  <si>
+    <t>word</t>
+  </si>
+  <si>
+    <t>单词</t>
+  </si>
+  <si>
+    <t>/wɜːd/</t>
+  </si>
+  <si>
+    <t>always</t>
+  </si>
+  <si>
+    <t>总是</t>
+  </si>
+  <si>
+    <t>adv.</t>
+  </si>
+  <si>
+    <t>B1-Unit 5</t>
+  </si>
+  <si>
+    <t>/ˈɔːlweɪz/</t>
+  </si>
+  <si>
+    <t>dinner</t>
+  </si>
+  <si>
+    <t>晚餐</t>
+  </si>
+  <si>
+    <t>/ˈdɪnə/</t>
+  </si>
+  <si>
+    <t>early</t>
+  </si>
+  <si>
+    <t>早的</t>
+  </si>
+  <si>
+    <t>/ˈɜːli/</t>
+  </si>
+  <si>
+    <t>learn</t>
+  </si>
+  <si>
+    <t>学习</t>
+  </si>
+  <si>
+    <t>/lɜːn/</t>
+  </si>
+  <si>
+    <t>morning</t>
+  </si>
+  <si>
+    <t>早上</t>
+  </si>
+  <si>
+    <t>/ˈmɔːnɪŋ/</t>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>夜晚</t>
+  </si>
+  <si>
+    <t>/naɪt/</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>学校</t>
+  </si>
+  <si>
+    <t>/skuːl/</t>
+  </si>
+  <si>
+    <t>teach</t>
+  </si>
+  <si>
+    <t>教</t>
+  </si>
+  <si>
+    <t>/tiːtʃ/</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>/taɪm/</t>
+  </si>
+  <si>
+    <t>watch</t>
+  </si>
+  <si>
+    <t>观看</t>
+  </si>
+  <si>
+    <t>/wɒtʃ/</t>
+  </si>
+  <si>
+    <t>center</t>
+  </si>
+  <si>
+    <t>中心</t>
+  </si>
+  <si>
+    <t>B1-Unit 6</t>
+  </si>
+  <si>
+    <t>/ˈsentə/</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>/ˈsɪti/</t>
+  </si>
+  <si>
+    <t>find</t>
+  </si>
+  <si>
+    <t>找到</t>
+  </si>
+  <si>
+    <t>/faɪnd/</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>房子</t>
+  </si>
+  <si>
+    <t>/haʊs/</t>
+  </si>
+  <si>
+    <t>market</t>
+  </si>
+  <si>
+    <t>市场</t>
+  </si>
+  <si>
+    <t>/ˈmɑːkɪt/</t>
+  </si>
+  <si>
+    <t>move</t>
+  </si>
+  <si>
+    <t>移动</t>
+  </si>
+  <si>
+    <t>/muːv/</t>
+  </si>
+  <si>
+    <t>place</t>
+  </si>
+  <si>
+    <t>地点</t>
+  </si>
+  <si>
+    <t>/pleɪs/</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>道路</t>
+  </si>
+  <si>
+    <t>/rəʊd/</t>
+  </si>
+  <si>
+    <t>town</t>
+  </si>
+  <si>
+    <t>城镇</t>
+  </si>
+  <si>
+    <t>/taʊn/</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>工作</t>
+  </si>
+  <si>
+    <t>/wɜːk/</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>国家；乡村</t>
+  </si>
+  <si>
+    <t>B1-Unit 7</t>
+  </si>
+  <si>
+    <t>/ˈkʌntri/</t>
+  </si>
+  <si>
+    <t>farm</t>
+  </si>
+  <si>
+    <t>农场</t>
+  </si>
+  <si>
+    <t>/fɑːm/</t>
+  </si>
+  <si>
+    <t>field</t>
+  </si>
+  <si>
+    <t>田地</t>
+  </si>
+  <si>
+    <t>/fiːld/</t>
+  </si>
+  <si>
+    <t>flower</t>
+  </si>
+  <si>
+    <t>花</t>
+  </si>
+  <si>
+    <t>/ˈflaʊə/</t>
+  </si>
+  <si>
+    <t>garden</t>
+  </si>
+  <si>
+    <t>花园</t>
+  </si>
+  <si>
+    <t>/ˈɡɑːdn/</t>
+  </si>
+  <si>
+    <t>hill</t>
+  </si>
+  <si>
+    <t>小山</t>
+  </si>
+  <si>
+    <t>/hɪl/</t>
+  </si>
+  <si>
+    <t>lake</t>
+  </si>
+  <si>
+    <t>湖泊</t>
+  </si>
+  <si>
+    <t>/leɪk/</t>
+  </si>
+  <si>
+    <t>mountain</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>/ˈmaʊntən/</t>
+  </si>
+  <si>
+    <t>tree</t>
+  </si>
+  <si>
+    <t>树</t>
+  </si>
+  <si>
+    <t>/triː/</t>
+  </si>
+  <si>
+    <t>world</t>
+  </si>
+  <si>
+    <t>世界</t>
+  </si>
+  <si>
+    <t>/wɜːld/</t>
+  </si>
+  <si>
+    <t>change</t>
+  </si>
+  <si>
+    <t>改变</t>
+  </si>
+  <si>
+    <t>B1-Unit 8</t>
+  </si>
+  <si>
+    <t>/tʃeɪndʒ/</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>颜色</t>
+  </si>
+  <si>
+    <t>/ˈkʌlə/</t>
+  </si>
+  <si>
+    <t>cool</t>
+  </si>
+  <si>
+    <t>凉爽的</t>
+  </si>
+  <si>
+    <t>/kuːl/</t>
+  </si>
+  <si>
+    <t>fall</t>
+  </si>
+  <si>
+    <t>落下；秋天</t>
+  </si>
+  <si>
+    <t>v./n.</t>
+  </si>
+  <si>
+    <t>/fɔːl/</t>
+  </si>
+  <si>
+    <t>hot</t>
+  </si>
+  <si>
+    <t>热的</t>
+  </si>
+  <si>
+    <t>/hɒt/</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>季节</t>
+  </si>
+  <si>
+    <t>/ˈsiːzn/</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>天空</t>
+  </si>
+  <si>
+    <t>/skaɪ/</t>
+  </si>
+  <si>
+    <t>snow</t>
+  </si>
+  <si>
+    <t>雪</t>
+  </si>
+  <si>
+    <t>/snəʊ/</t>
+  </si>
+  <si>
+    <t>warm</t>
+  </si>
+  <si>
+    <t>温暖的</t>
+  </si>
+  <si>
+    <t>/wɔːm/</t>
+  </si>
+  <si>
+    <t>weather</t>
+  </si>
+  <si>
+    <t>天气</t>
+  </si>
+  <si>
+    <t>/ˈweðə/</t>
+  </si>
+  <si>
+    <t>buy</t>
+  </si>
+  <si>
+    <t>买</t>
+  </si>
+  <si>
+    <t>B1-Unit 9</t>
+  </si>
+  <si>
+    <t>/baɪ/</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>花费</t>
+  </si>
+  <si>
+    <t>/kɒst/</t>
+  </si>
+  <si>
+    <t>dress</t>
+  </si>
+  <si>
+    <t>连衣裙</t>
+  </si>
+  <si>
+    <t>/dres/</t>
+  </si>
+  <si>
+    <t>jeans</t>
+  </si>
+  <si>
+    <t>牛仔裤</t>
+  </si>
+  <si>
+    <t>/dʒiːnz/</t>
+  </si>
+  <si>
+    <t>pay</t>
+  </si>
+  <si>
+    <t>支付</t>
+  </si>
+  <si>
+    <t>/peɪ/</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>卖</t>
+  </si>
+  <si>
+    <t>/sel/</t>
+  </si>
+  <si>
+    <t>shirt</t>
+  </si>
+  <si>
+    <t>衬衫</t>
+  </si>
+  <si>
+    <t>/ʃɜːt/</t>
+  </si>
+  <si>
+    <t>shop</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>/ʃɒp/</t>
+  </si>
+  <si>
+    <t>spend</t>
+  </si>
+  <si>
+    <t>花费（时间/钱）</t>
+  </si>
+  <si>
+    <t>/spend/</t>
+  </si>
+  <si>
+    <t>wear</t>
+  </si>
+  <si>
+    <t>穿</t>
+  </si>
+  <si>
+    <t>/weə/</t>
+  </si>
+  <si>
+    <t>body</t>
+  </si>
+  <si>
+    <t>身体</t>
+  </si>
+  <si>
+    <t>B1-Unit 10</t>
+  </si>
+  <si>
+    <t>/ˈbɒdi/</t>
+  </si>
+  <si>
+    <t>ear</t>
+  </si>
+  <si>
+    <t>耳朵</t>
+  </si>
+  <si>
+    <t>/ɪə/</t>
+  </si>
+  <si>
+    <t>eye</t>
+  </si>
+  <si>
+    <t>眼睛</t>
+  </si>
+  <si>
+    <t>/aɪ/</t>
+  </si>
+  <si>
+    <t>face</t>
+  </si>
+  <si>
+    <t>脸</t>
+  </si>
+  <si>
+    <t>/feɪs/</t>
+  </si>
+  <si>
+    <t>foot</t>
+  </si>
+  <si>
+    <t>脚</t>
+  </si>
+  <si>
+    <t>/fʊt/</t>
+  </si>
+  <si>
+    <t>hair</t>
+  </si>
+  <si>
+    <t>头发</t>
+  </si>
+  <si>
+    <t>/heə/</t>
+  </si>
+  <si>
+    <t>hand</t>
+  </si>
+  <si>
+    <t>手</t>
+  </si>
+  <si>
+    <t>/hænd/</t>
+  </si>
+  <si>
+    <t>mouth</t>
+  </si>
+  <si>
+    <t>嘴</t>
+  </si>
+  <si>
+    <t>/maʊθ/</t>
+  </si>
+  <si>
+    <t>nose</t>
+  </si>
+  <si>
+    <t>鼻子</t>
+  </si>
+  <si>
+    <t>/nəʊz/</t>
+  </si>
+  <si>
+    <t>tooth</t>
+  </si>
+  <si>
+    <t>牙齿</t>
+  </si>
+  <si>
+    <t>/tuːθ/</t>
+  </si>
+  <si>
+    <t>glass</t>
+  </si>
+  <si>
+    <t>玻璃；杯子</t>
+  </si>
+  <si>
+    <t>B1-Unit 11</t>
+  </si>
+  <si>
+    <t>/ɡlɑːs/</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>钥匙</t>
+  </si>
+  <si>
+    <t>/kiː/</t>
+  </si>
+  <si>
+    <t>light</t>
+  </si>
+  <si>
+    <t>光；灯</t>
+  </si>
+  <si>
+    <t>/laɪt/</t>
+  </si>
+  <si>
+    <t>money</t>
+  </si>
+  <si>
+    <t>钱</t>
+  </si>
+  <si>
+    <t>/ˈmʌni/</t>
+  </si>
+  <si>
+    <t>paper</t>
+  </si>
+  <si>
+    <t>纸</t>
+  </si>
+  <si>
+    <t>/ˈpeɪpə/</t>
+  </si>
+  <si>
+    <t>pen</t>
+  </si>
+  <si>
+    <t>钢笔</t>
+  </si>
+  <si>
+    <t>/pen/</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>/fəʊn/</t>
+  </si>
+  <si>
+    <t>picture</t>
+  </si>
+  <si>
+    <t>图片</t>
+  </si>
+  <si>
+    <t>/ˈpɪktʃə/</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>桌子</t>
+  </si>
+  <si>
+    <t>/ˈteɪbl/</t>
+  </si>
+  <si>
+    <t>thing</t>
+  </si>
+  <si>
+    <t>事物</t>
+  </si>
+  <si>
+    <t>/θɪŋ/</t>
+  </si>
+  <si>
+    <t>act</t>
+  </si>
+  <si>
+    <t>行动；表演</t>
+  </si>
+  <si>
+    <t>B1-Unit 12</t>
+  </si>
+  <si>
+    <t>/ækt/</t>
+  </si>
+  <si>
+    <t>bring</t>
+  </si>
+  <si>
+    <t>带来</t>
+  </si>
+  <si>
+    <t>/brɪŋ/</t>
+  </si>
+  <si>
+    <t>glad</t>
+  </si>
+  <si>
+    <t>高兴的</t>
+  </si>
+  <si>
+    <t>/ɡlæd/</t>
+  </si>
+  <si>
+    <t>lesson</t>
+  </si>
+  <si>
+    <t>课</t>
+  </si>
+  <si>
+    <t>/ˈlesn/</t>
+  </si>
+  <si>
+    <t>listen</t>
+  </si>
+  <si>
+    <t>听</t>
+  </si>
+  <si>
+    <t>/ˈlɪsn/</t>
+  </si>
+  <si>
+    <t>pencil</t>
+  </si>
+  <si>
+    <t>铅笔</t>
+  </si>
+  <si>
+    <t>/ˈpensl/</t>
+  </si>
+  <si>
+    <t>talk</t>
+  </si>
+  <si>
+    <t>谈话</t>
+  </si>
+  <si>
+    <t>/tɔːk/</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>走路</t>
+  </si>
+  <si>
+    <t>/wɔːk/</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>年</t>
+  </si>
+  <si>
+    <t>/jɪə/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -124,6 +1392,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -145,11 +1428,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -372,7 +1661,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -383,64 +1672,2410 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E5" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E6" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/my_words.xlsx
+++ b/my_words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiwi_\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{638DBBAF-0131-4400-8F10-6DB82119FDF5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B3A693-4DA9-4435-A6D8-5363D33696FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20378" windowHeight="8760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,24 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="440">
   <si>
     <t>en</t>
   </si>
   <si>
     <t>cn</t>
-  </si>
-  <si>
-    <t>unit</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>phonetic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>type</t>
@@ -1358,16 +1346,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1376,20 +1358,6 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1428,15 +1396,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1661,2425 +1626,2408 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="C9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>34</v>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="C17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="C18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="C19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="C20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="C21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="E22" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="B23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="C23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="C24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="C27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="C29" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="D29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B30" s="5" t="s">
+      <c r="A30" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="C31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="5" t="s">
+      <c r="C32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="C33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="C35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="C37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="5" t="s">
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="5" t="s">
+      <c r="C39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="C40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="C41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="5" t="s">
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>133</v>
       </c>
+      <c r="E42" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="A43" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="B43" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="C44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="5" t="s">
+      <c r="C45" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="5" t="s">
+      <c r="C46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" s="5" t="s">
+      <c r="C47" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E48" s="5" t="s">
+      <c r="C48" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E49" s="5" t="s">
+      <c r="C49" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" s="5" t="s">
+      <c r="C50" s="2" t="s">
         <v>158</v>
       </c>
+      <c r="D50" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="A51" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="B51" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="5" t="s">
+      <c r="C51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" s="5" t="s">
+      <c r="C52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>165</v>
       </c>
+      <c r="E52" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="B53" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="C53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E54" s="5" t="s">
+      <c r="C54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E55" s="5" t="s">
+      <c r="C55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E56" s="5" t="s">
+      <c r="C56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E57" s="5" t="s">
+    </row>
+    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="5" t="s">
+      <c r="B58" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E58" s="5" t="s">
+      <c r="C58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E59" s="5" t="s">
+      <c r="C59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E60" s="5" t="s">
+      <c r="C60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E61" s="5" t="s">
+      <c r="C61" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="E62" s="5" t="s">
+      <c r="C62" s="2" t="s">
         <v>195</v>
       </c>
+      <c r="D62" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E64" s="5" t="s">
+      <c r="C64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E65" s="5" t="s">
+      <c r="C65" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="C66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E67" s="5" t="s">
+      <c r="C67" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E68" s="5" t="s">
+      <c r="C68" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E69" s="5" t="s">
+      <c r="C69" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E70" s="5" t="s">
+      <c r="C70" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E71" s="5" t="s">
+      <c r="C71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E72" s="5" t="s">
+      <c r="C72" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>227</v>
       </c>
+      <c r="E72" s="2" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="A73" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D73" s="5" t="s">
+      <c r="B73" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="C73" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E74" s="5" t="s">
+      <c r="C74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E75" s="5" t="s">
+      <c r="C75" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E76" s="5" t="s">
+      <c r="C76" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C77" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E77" s="5" t="s">
+      <c r="C77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C78" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E78" s="5" t="s">
+      <c r="C78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="5" t="s">
+      <c r="A79" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E79" s="5" t="s">
+      <c r="C79" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C80" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E80" s="5" t="s">
+      <c r="C80" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="5" t="s">
+      <c r="A81" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C81" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E81" s="5" t="s">
+      <c r="C81" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E82" s="5" t="s">
+      <c r="C82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>258</v>
       </c>
+      <c r="E82" s="2" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B83" s="5" t="s">
+      <c r="A83" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D83" s="5" t="s">
+      <c r="B83" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="C83" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E84" s="5" t="s">
+      <c r="C84" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B85" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C85" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E85" s="5" t="s">
+      <c r="C85" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C86" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E86" s="5" t="s">
+      <c r="C86" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C87" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E87" s="5" t="s">
+      <c r="C87" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C88" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E88" s="5" t="s">
+      <c r="C88" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E89" s="5" t="s">
+      <c r="C89" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C90" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E90" s="5" t="s">
+      <c r="C90" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="5" t="s">
+      <c r="A91" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C91" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E91" s="5" t="s">
+      <c r="C91" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C92" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E92" s="5" t="s">
+      <c r="C92" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>289</v>
       </c>
+      <c r="E92" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="93" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B93" s="5" t="s">
+      <c r="A93" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C93" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" s="5" t="s">
+      <c r="B93" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="C93" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C94" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E94" s="5" t="s">
+      <c r="C94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E95" s="5" t="s">
+      <c r="C95" s="2" t="s">
         <v>299</v>
       </c>
+      <c r="D95" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B96" s="5" t="s">
+      <c r="A96" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="B96" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D96" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E96" s="5" t="s">
+      <c r="C96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="5" t="s">
+      <c r="A97" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E97" s="5" t="s">
+      <c r="C97" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="5" t="s">
+      <c r="A98" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E98" s="5" t="s">
+      <c r="C98" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="5" t="s">
+      <c r="A99" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E99" s="5" t="s">
+      <c r="C99" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E100" s="5" t="s">
+      <c r="C100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="5" t="s">
+      <c r="A101" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C101" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E101" s="5" t="s">
+      <c r="C101" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C102" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E102" s="5" t="s">
+      <c r="C102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>321</v>
       </c>
+      <c r="E102" s="2" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="103" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="A103" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C103" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="5" t="s">
+      <c r="B103" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="C103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="5" t="s">
+      <c r="A104" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C104" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E104" s="5" t="s">
+      <c r="C104" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="5" t="s">
+      <c r="A105" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="C105" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E105" s="5" t="s">
+      <c r="C105" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C106" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E106" s="5" t="s">
+      <c r="C106" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C107" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E107" s="5" t="s">
+      <c r="C107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="5" t="s">
+      <c r="A108" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C108" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E108" s="5" t="s">
+      <c r="C108" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="5" t="s">
+      <c r="A109" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E109" s="5" t="s">
+      <c r="C109" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E110" s="5" t="s">
+      <c r="C110" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C111" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E111" s="5" t="s">
+      <c r="C111" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="5" t="s">
+      <c r="A112" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C112" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="E112" s="5" t="s">
+      <c r="C112" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>352</v>
       </c>
+      <c r="E112" s="2" t="s">
+        <v>353</v>
+      </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="A113" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D113" s="5" t="s">
+      <c r="B113" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="C113" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C114" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E114" s="5" t="s">
+      <c r="C114" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="5" t="s">
+      <c r="A115" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C115" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E115" s="5" t="s">
+      <c r="C115" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="5" t="s">
+      <c r="A116" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E116" s="5" t="s">
+      <c r="C116" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="5" t="s">
+      <c r="A117" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B117" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C117" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E117" s="5" t="s">
+      <c r="C117" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E118" s="5" t="s">
+      <c r="C118" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="5" t="s">
+      <c r="A119" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C119" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E119" s="5" t="s">
+      <c r="C119" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="5" t="s">
+      <c r="A120" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E120" s="5" t="s">
+      <c r="C120" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="5" t="s">
+      <c r="A121" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B121" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C121" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E121" s="5" t="s">
+      <c r="C121" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C122" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="E122" s="5" t="s">
+      <c r="C122" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>383</v>
       </c>
+      <c r="E122" s="2" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="B123" s="5" t="s">
+      <c r="A123" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="C123" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D123" s="5" t="s">
+      <c r="B123" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="E123" s="5" t="s">
+      <c r="C123" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="5" t="s">
+      <c r="A124" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C124" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E124" s="5" t="s">
+      <c r="C124" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="5" t="s">
+      <c r="A125" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C125" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E125" s="5" t="s">
+      <c r="C125" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="5" t="s">
+      <c r="A126" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C126" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E126" s="5" t="s">
+      <c r="C126" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E126" s="2" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="5" t="s">
+      <c r="A127" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C127" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E127" s="5" t="s">
+      <c r="C127" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="5" t="s">
+      <c r="A128" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B128" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E128" s="5" t="s">
+      <c r="C128" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="5" t="s">
+      <c r="A129" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C129" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E129" s="5" t="s">
+      <c r="C129" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B130" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C130" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E130" s="5" t="s">
+      <c r="C130" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B131" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E131" s="5" t="s">
+      <c r="C131" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="5" t="s">
+      <c r="A132" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B132" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C132" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E132" s="5" t="s">
+      <c r="C132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="2" t="s">
         <v>414</v>
       </c>
+      <c r="E132" s="2" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="133" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A133" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="B133" s="5" t="s">
+      <c r="A133" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C133" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D133" s="5" t="s">
+      <c r="B133" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="E133" s="5" t="s">
+      <c r="C133" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A134" s="5" t="s">
+      <c r="A134" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="B134" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C134" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E134" s="5" t="s">
+      <c r="C134" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="B135" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C135" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E135" s="5" t="s">
+      <c r="C135" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B136" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C136" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E136" s="5" t="s">
+      <c r="C136" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A137" s="5" t="s">
+      <c r="A137" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B137" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C137" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E137" s="5" t="s">
+      <c r="C137" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B139" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C138" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E138" s="5" t="s">
+      <c r="C139" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
     <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="5" t="s">
+      <c r="A140" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C140" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E140" s="5" t="s">
+      <c r="C140" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="5" t="s">
+      <c r="A141" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C141" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E141" s="5" t="s">
+      <c r="C141" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
